--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,185 +656,197 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E8" s="3">
         <v>900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4700</v>
       </c>
-      <c r="H8" s="3">
-        <v>60800</v>
-      </c>
       <c r="I8" s="3">
-        <v>21300</v>
+        <v>61200</v>
       </c>
       <c r="J8" s="3">
+        <v>21500</v>
+      </c>
+      <c r="K8" s="3">
         <v>41600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>45500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6000</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
-        <v>4200</v>
-      </c>
       <c r="F9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G9" s="3">
         <v>1800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>9300</v>
       </c>
-      <c r="I9" s="3">
-        <v>3000</v>
-      </c>
       <c r="J9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K9" s="3">
         <v>9200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1900</v>
       </c>
-      <c r="H10" s="3">
-        <v>51500</v>
-      </c>
       <c r="I10" s="3">
-        <v>18300</v>
+        <v>51900</v>
       </c>
       <c r="J10" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K10" s="3">
         <v>32500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,46 +861,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1800</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +941,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +982,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -977,17 +999,17 @@
       <c r="F15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="3">
-        <v>49000</v>
+      <c r="G15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H15" s="3">
+        <v>49400</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="J15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -995,14 +1017,17 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,84 +1039,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
         <v>4800</v>
       </c>
-      <c r="E17" s="3">
-        <v>6600</v>
-      </c>
       <c r="F17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4500</v>
       </c>
-      <c r="H17" s="3">
-        <v>16300</v>
-      </c>
       <c r="I17" s="3">
+        <v>16400</v>
+      </c>
+      <c r="J17" s="3">
         <v>4400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
-        <v>44400</v>
-      </c>
       <c r="I18" s="3">
-        <v>16900</v>
+        <v>44700</v>
       </c>
       <c r="J18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K18" s="3">
         <v>27200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,46 +1138,50 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>200</v>
       </c>
       <c r="L20" s="3">
+        <v>200</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1158,40 +1194,43 @@
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3">
         <v>2300</v>
       </c>
-      <c r="H21" s="3">
-        <v>48800</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="I21" s="3">
+        <v>49100</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K21" s="3">
         <v>27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -1214,81 +1253,87 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
-        <v>-3900</v>
-      </c>
       <c r="F23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="G23" s="3">
         <v>900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2100</v>
       </c>
-      <c r="H23" s="3">
-        <v>48600</v>
-      </c>
       <c r="I23" s="3">
-        <v>18400</v>
+        <v>49000</v>
       </c>
       <c r="J23" s="3">
+        <v>18500</v>
+      </c>
+      <c r="K23" s="3">
         <v>27400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>34700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1296,8 +1341,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1382,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-2600</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="F26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G26" s="3">
         <v>700</v>
       </c>
-      <c r="G26" s="3">
-        <v>1700</v>
-      </c>
       <c r="H26" s="3">
-        <v>47300</v>
+        <v>1800</v>
       </c>
       <c r="I26" s="3">
-        <v>17700</v>
+        <v>47600</v>
       </c>
       <c r="J26" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K26" s="3">
         <v>27400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-2600</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="F27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G27" s="3">
         <v>700</v>
       </c>
-      <c r="G27" s="3">
-        <v>1700</v>
-      </c>
       <c r="H27" s="3">
-        <v>47300</v>
+        <v>1800</v>
       </c>
       <c r="I27" s="3">
-        <v>17700</v>
+        <v>47600</v>
       </c>
       <c r="J27" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K27" s="3">
         <v>27400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1505,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1546,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1587,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,84 +1628,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>-200</v>
       </c>
       <c r="L32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-2600</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="F33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G33" s="3">
         <v>700</v>
       </c>
-      <c r="G33" s="3">
-        <v>1700</v>
-      </c>
       <c r="H33" s="3">
-        <v>47300</v>
+        <v>1800</v>
       </c>
       <c r="I33" s="3">
-        <v>17700</v>
+        <v>47600</v>
       </c>
       <c r="J33" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K33" s="3">
         <v>27400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1751,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-2600</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="F35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G35" s="3">
         <v>700</v>
       </c>
-      <c r="G35" s="3">
-        <v>1700</v>
-      </c>
       <c r="H35" s="3">
-        <v>47300</v>
+        <v>1800</v>
       </c>
       <c r="I35" s="3">
-        <v>17700</v>
+        <v>47600</v>
       </c>
       <c r="J35" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K35" s="3">
         <v>27400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +1857,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,28 +1874,29 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>97200</v>
+        <v>96600</v>
       </c>
       <c r="E41" s="3">
-        <v>105200</v>
+        <v>97800</v>
       </c>
       <c r="F41" s="3">
-        <v>105200</v>
+        <v>106000</v>
       </c>
       <c r="G41" s="3">
-        <v>98300</v>
+        <v>106000</v>
       </c>
       <c r="H41" s="3">
-        <v>97100</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
+        <v>99000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>97700</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
@@ -1827,17 +1913,20 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1853,8 +1942,8 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -1865,8 +1954,11 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1879,12 +1971,12 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>200</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1903,29 +1995,32 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>7700</v>
+        <v>5800</v>
       </c>
       <c r="E44" s="3">
-        <v>9700</v>
+        <v>7800</v>
       </c>
       <c r="F44" s="3">
-        <v>11600</v>
+        <v>9800</v>
       </c>
       <c r="G44" s="3">
-        <v>10700</v>
+        <v>11700</v>
       </c>
       <c r="H44" s="3">
+        <v>10800</v>
+      </c>
+      <c r="I44" s="3">
         <v>10600</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,28 +2036,31 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1400</v>
+        <v>6600</v>
       </c>
       <c r="E45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
-        <v>5600</v>
-      </c>
       <c r="H45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+        <v>5700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>6000</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1979,28 +2077,31 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>106800</v>
+        <v>110900</v>
       </c>
       <c r="E46" s="3">
-        <v>116300</v>
+        <v>107500</v>
       </c>
       <c r="F46" s="3">
-        <v>119500</v>
+        <v>117100</v>
       </c>
       <c r="G46" s="3">
-        <v>114900</v>
+        <v>120300</v>
       </c>
       <c r="H46" s="3">
-        <v>113600</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
+        <v>115700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>114400</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
@@ -2017,17 +2118,20 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2147,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2055,29 +2159,32 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6700</v>
+        <v>7100</v>
       </c>
       <c r="E48" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1000</v>
       </c>
-      <c r="G48" s="3">
-        <v>1100</v>
-      </c>
       <c r="H48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,31 +2200,34 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2131,8 +2241,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2282,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,28 +2323,31 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>18300</v>
+        <v>15800</v>
       </c>
       <c r="E52" s="3">
-        <v>17000</v>
+        <v>18500</v>
       </c>
       <c r="F52" s="3">
-        <v>15600</v>
+        <v>17100</v>
       </c>
       <c r="G52" s="3">
-        <v>15600</v>
+        <v>15700</v>
       </c>
       <c r="H52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+        <v>15700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15700</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2364,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,28 +2405,31 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>131900</v>
+        <v>136100</v>
       </c>
       <c r="E54" s="3">
-        <v>134500</v>
+        <v>132800</v>
       </c>
       <c r="F54" s="3">
-        <v>136100</v>
+        <v>135400</v>
       </c>
       <c r="G54" s="3">
-        <v>131600</v>
+        <v>137000</v>
       </c>
       <c r="H54" s="3">
-        <v>130000</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
+        <v>132500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>130900</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
@@ -2321,8 +2446,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2465,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,8 +2482,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2362,20 +2492,20 @@
         <v>0</v>
       </c>
       <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2521,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2429,29 +2562,32 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,29 +2603,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1800</v>
+        <v>3900</v>
       </c>
       <c r="E60" s="3">
         <v>1800</v>
       </c>
       <c r="F60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2644,11 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2543,29 +2685,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
         <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G62" s="3">
         <v>0</v>
       </c>
       <c r="H62" s="3">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,8 +2726,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +2767,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +2808,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,13 +2849,16 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1900</v>
+        <v>4000</v>
       </c>
       <c r="E66" s="3">
         <v>1900</v>
@@ -2710,13 +2867,13 @@
         <v>1900</v>
       </c>
       <c r="G66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H66" s="3">
         <v>2700</v>
       </c>
-      <c r="H66" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
+      <c r="I66" s="3">
+        <v>2900</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
@@ -2733,8 +2890,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +2909,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +2948,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +2989,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3030,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,28 +3071,31 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>104100</v>
+        <v>106000</v>
       </c>
       <c r="E72" s="3">
-        <v>106800</v>
+        <v>104800</v>
       </c>
       <c r="F72" s="3">
-        <v>109600</v>
+        <v>107500</v>
       </c>
       <c r="G72" s="3">
-        <v>108900</v>
+        <v>110300</v>
       </c>
       <c r="H72" s="3">
-        <v>107200</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
+        <v>109700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>107900</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
@@ -2939,8 +3112,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3153,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3194,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,28 +3235,31 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>130000</v>
+        <v>132100</v>
       </c>
       <c r="E76" s="3">
-        <v>132600</v>
+        <v>130900</v>
       </c>
       <c r="F76" s="3">
-        <v>134200</v>
+        <v>133500</v>
       </c>
       <c r="G76" s="3">
-        <v>128900</v>
+        <v>135100</v>
       </c>
       <c r="H76" s="3">
-        <v>127200</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
+        <v>129800</v>
+      </c>
+      <c r="I76" s="3">
+        <v>128000</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
@@ -3091,8 +3276,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3317,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-2600</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="F81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="G81" s="3">
         <v>700</v>
       </c>
-      <c r="G81" s="3">
-        <v>1700</v>
-      </c>
       <c r="H81" s="3">
-        <v>47300</v>
+        <v>1800</v>
       </c>
       <c r="I81" s="3">
-        <v>17700</v>
+        <v>47600</v>
       </c>
       <c r="J81" s="3">
+        <v>17800</v>
+      </c>
+      <c r="K81" s="3">
         <v>27400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,8 +3423,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3240,32 +3438,35 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
-        <v>200</v>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3503,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3544,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +3585,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +3626,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,8 +3667,11 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3468,14 +3684,14 @@
       <c r="F89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G89" s="3">
-        <v>45100</v>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
-        <v>43700</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>45400</v>
+      </c>
+      <c r="I89" s="3">
+        <v>44000</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3483,17 +3699,20 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>1700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,8 +3727,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3546,8 +3766,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +3807,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,8 +3848,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3636,32 +3865,35 @@
       <c r="F94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-16100</v>
       </c>
-      <c r="H94" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +3908,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +3947,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +3988,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4029,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,8 +4070,11 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -3854,20 +4099,23 @@
       <c r="J100" s="3">
         <v>0</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,8 +4152,11 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3918,14 +4169,14 @@
       <c r="F102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G102" s="3">
-        <v>29000</v>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H102" s="3">
-        <v>27700</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+        <v>29200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>27900</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
@@ -3933,13 +4184,16 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,197 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E8" s="3">
         <v>4900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4700</v>
       </c>
-      <c r="I8" s="3">
-        <v>61200</v>
-      </c>
       <c r="J8" s="3">
+        <v>60800</v>
+      </c>
+      <c r="K8" s="3">
         <v>21500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>45500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6000</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E9" s="3">
         <v>2000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2100</v>
       </c>
-      <c r="F9" s="3">
-        <v>4300</v>
-      </c>
       <c r="G9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H9" s="3">
         <v>1800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>9300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1900</v>
       </c>
-      <c r="I10" s="3">
-        <v>51900</v>
-      </c>
       <c r="J10" s="3">
+        <v>51500</v>
+      </c>
+      <c r="K10" s="3">
         <v>18400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,49 +875,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,8 +961,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -985,8 +1005,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1002,17 +1025,17 @@
       <c r="G15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H15" s="3">
-        <v>49400</v>
+      <c r="H15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I15" s="3">
+        <v>49100</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1020,14 +1043,17 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1040,90 +1066,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>7400</v>
       </c>
       <c r="E17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F17" s="3">
         <v>4800</v>
       </c>
-      <c r="F17" s="3">
-        <v>6700</v>
-      </c>
       <c r="G17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H17" s="3">
         <v>3800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4500</v>
       </c>
-      <c r="I17" s="3">
-        <v>16400</v>
-      </c>
       <c r="J17" s="3">
+        <v>16300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-4000</v>
       </c>
       <c r="E18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
-        <v>44700</v>
-      </c>
       <c r="J18" s="3">
+        <v>44500</v>
+      </c>
+      <c r="K18" s="3">
         <v>17000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1139,49 +1172,53 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>600</v>
       </c>
       <c r="E20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>200</v>
       </c>
       <c r="M20" s="3">
+        <v>200</v>
+      </c>
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1197,43 +1234,46 @@
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>2300</v>
       </c>
-      <c r="I21" s="3">
-        <v>49100</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="J21" s="3">
+        <v>48800</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>27500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>34700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1100</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1256,87 +1296,93 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-4000</v>
-      </c>
       <c r="G23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="H23" s="3">
         <v>900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2100</v>
       </c>
-      <c r="I23" s="3">
-        <v>49000</v>
-      </c>
       <c r="J23" s="3">
+        <v>48600</v>
+      </c>
+      <c r="K23" s="3">
         <v>18500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>34700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-1400</v>
       </c>
       <c r="E24" s="3">
+        <v>200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1344,8 +1390,11 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1385,90 +1434,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-2000</v>
       </c>
       <c r="E26" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="G26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H26" s="3">
         <v>700</v>
       </c>
-      <c r="H26" s="3">
-        <v>1800</v>
-      </c>
       <c r="I26" s="3">
-        <v>47600</v>
+        <v>1700</v>
       </c>
       <c r="J26" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K26" s="3">
         <v>17800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>27400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-2000</v>
       </c>
       <c r="E27" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="F27" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="G27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H27" s="3">
         <v>700</v>
       </c>
-      <c r="H27" s="3">
-        <v>1800</v>
-      </c>
       <c r="I27" s="3">
-        <v>47600</v>
+        <v>1700</v>
       </c>
       <c r="J27" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K27" s="3">
         <v>17800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>27400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1508,8 +1566,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1549,8 +1610,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1590,8 +1654,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1631,90 +1698,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>-200</v>
       </c>
       <c r="M32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-2000</v>
       </c>
       <c r="E33" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="F33" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="G33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H33" s="3">
         <v>700</v>
       </c>
-      <c r="H33" s="3">
-        <v>1800</v>
-      </c>
       <c r="I33" s="3">
-        <v>47600</v>
+        <v>1700</v>
       </c>
       <c r="J33" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K33" s="3">
         <v>17800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>27400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1754,95 +1830,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-2000</v>
       </c>
       <c r="E35" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="F35" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="G35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H35" s="3">
         <v>700</v>
       </c>
-      <c r="H35" s="3">
-        <v>1800</v>
-      </c>
       <c r="I35" s="3">
-        <v>47600</v>
+        <v>1700</v>
       </c>
       <c r="J35" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K35" s="3">
         <v>17800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>27400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1858,8 +1943,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1875,31 +1961,32 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>96600</v>
+        <v>92000</v>
       </c>
       <c r="E41" s="3">
-        <v>97800</v>
+        <v>96000</v>
       </c>
       <c r="F41" s="3">
-        <v>106000</v>
+        <v>97200</v>
       </c>
       <c r="G41" s="3">
-        <v>106000</v>
+        <v>105300</v>
       </c>
       <c r="H41" s="3">
-        <v>99000</v>
+        <v>105300</v>
       </c>
       <c r="I41" s="3">
-        <v>97700</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>98400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>97100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1916,20 +2003,23 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>700</v>
       </c>
       <c r="E42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F42" s="3">
         <v>500</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G42" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,8 +2035,8 @@
       <c r="K42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -1957,8 +2047,11 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1974,12 +2067,12 @@
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1998,32 +2091,35 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E44" s="3">
         <v>5800</v>
       </c>
-      <c r="E44" s="3">
-        <v>7800</v>
-      </c>
       <c r="F44" s="3">
-        <v>9800</v>
+        <v>7700</v>
       </c>
       <c r="G44" s="3">
-        <v>11700</v>
+        <v>9700</v>
       </c>
       <c r="H44" s="3">
-        <v>10800</v>
+        <v>11600</v>
       </c>
       <c r="I44" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J44" s="3">
         <v>10600</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,31 +2135,34 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6600</v>
+        <v>5100</v>
       </c>
       <c r="E45" s="3">
-        <v>1500</v>
+        <v>6500</v>
       </c>
       <c r="F45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
-        <v>5700</v>
-      </c>
       <c r="I45" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>5600</v>
+      </c>
+      <c r="J45" s="3">
+        <v>5900</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -2080,31 +2179,34 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>110900</v>
+        <v>102100</v>
       </c>
       <c r="E46" s="3">
-        <v>107500</v>
+        <v>110200</v>
       </c>
       <c r="F46" s="3">
-        <v>117100</v>
+        <v>106900</v>
       </c>
       <c r="G46" s="3">
-        <v>120300</v>
+        <v>116400</v>
       </c>
       <c r="H46" s="3">
-        <v>115700</v>
+        <v>119600</v>
       </c>
       <c r="I46" s="3">
-        <v>114400</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>114900</v>
+      </c>
+      <c r="J46" s="3">
+        <v>113700</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -2121,19 +2223,22 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>3300</v>
       </c>
       <c r="E47" s="3">
         <v>100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
+      <c r="F47" s="3">
+        <v>100</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
@@ -2150,8 +2255,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2162,32 +2267,35 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="E48" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="F48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G48" s="3">
         <v>1200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1000</v>
       </c>
-      <c r="H48" s="3">
-        <v>1200</v>
-      </c>
       <c r="I48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,16 +2311,19 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
         <v>500</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+      <c r="E49" s="3">
+        <v>500</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>3</v>
@@ -2229,8 +2340,8 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2244,8 +2355,11 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2285,8 +2399,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2326,31 +2443,34 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15800</v>
+        <v>19000</v>
       </c>
       <c r="E52" s="3">
-        <v>18500</v>
+        <v>17500</v>
       </c>
       <c r="F52" s="3">
-        <v>17100</v>
+        <v>18300</v>
       </c>
       <c r="G52" s="3">
-        <v>15700</v>
+        <v>17000</v>
       </c>
       <c r="H52" s="3">
-        <v>15700</v>
+        <v>15600</v>
       </c>
       <c r="I52" s="3">
-        <v>15700</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>15600</v>
+      </c>
+      <c r="J52" s="3">
+        <v>15600</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2367,8 +2487,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2408,31 +2531,34 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>136100</v>
+        <v>131900</v>
       </c>
       <c r="E54" s="3">
-        <v>132800</v>
+        <v>135300</v>
       </c>
       <c r="F54" s="3">
-        <v>135400</v>
+        <v>132000</v>
       </c>
       <c r="G54" s="3">
-        <v>137000</v>
+        <v>134600</v>
       </c>
       <c r="H54" s="3">
-        <v>132500</v>
+        <v>136200</v>
       </c>
       <c r="I54" s="3">
-        <v>130900</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>131700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>130100</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2449,8 +2575,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2466,8 +2595,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2483,32 +2613,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2524,8 +2655,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2565,32 +2699,35 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2500</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,32 +2743,35 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
-      </c>
-      <c r="E60" s="3">
-        <v>1800</v>
       </c>
       <c r="F60" s="3">
         <v>1800</v>
       </c>
       <c r="G60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H60" s="3">
         <v>1900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2800</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2787,11 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2688,8 +2831,11 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2697,23 +2843,23 @@
         <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2729,8 +2875,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2770,8 +2919,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2811,8 +2963,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2852,16 +3007,19 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4000</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1900</v>
       </c>
       <c r="F66" s="3">
         <v>1900</v>
@@ -2870,13 +3028,13 @@
         <v>1900</v>
       </c>
       <c r="H66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I66" s="3">
         <v>2700</v>
       </c>
-      <c r="I66" s="3">
-        <v>2900</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>2800</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2893,8 +3051,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2910,8 +3071,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2951,8 +3113,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2992,8 +3157,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3033,8 +3201,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3074,31 +3245,34 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>106000</v>
+        <v>103300</v>
       </c>
       <c r="E72" s="3">
-        <v>104800</v>
+        <v>105300</v>
       </c>
       <c r="F72" s="3">
-        <v>107500</v>
+        <v>104200</v>
       </c>
       <c r="G72" s="3">
-        <v>110300</v>
+        <v>106800</v>
       </c>
       <c r="H72" s="3">
         <v>109700</v>
       </c>
       <c r="I72" s="3">
-        <v>107900</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>109000</v>
+      </c>
+      <c r="J72" s="3">
+        <v>107300</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -3115,8 +3289,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3156,8 +3333,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3197,8 +3377,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3238,31 +3421,34 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>132100</v>
+        <v>129500</v>
       </c>
       <c r="E76" s="3">
-        <v>130900</v>
+        <v>131300</v>
       </c>
       <c r="F76" s="3">
-        <v>133500</v>
+        <v>130100</v>
       </c>
       <c r="G76" s="3">
-        <v>135100</v>
+        <v>132700</v>
       </c>
       <c r="H76" s="3">
-        <v>129800</v>
+        <v>134300</v>
       </c>
       <c r="I76" s="3">
-        <v>128000</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>129000</v>
+      </c>
+      <c r="J76" s="3">
+        <v>127200</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3279,8 +3465,11 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3320,95 +3509,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-2000</v>
       </c>
       <c r="E81" s="3">
-        <v>-2700</v>
+        <v>1100</v>
       </c>
       <c r="F81" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="G81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="H81" s="3">
         <v>700</v>
       </c>
-      <c r="H81" s="3">
-        <v>1800</v>
-      </c>
       <c r="I81" s="3">
-        <v>47600</v>
+        <v>1700</v>
       </c>
       <c r="J81" s="3">
+        <v>47300</v>
+      </c>
+      <c r="K81" s="3">
         <v>17800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>27400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3424,8 +3622,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3441,11 +3640,11 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
-        <v>300</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3456,17 +3655,20 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3506,8 +3708,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3547,8 +3752,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3588,8 +3796,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3629,8 +3840,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3670,8 +3884,11 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -3687,11 +3904,11 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3">
-        <v>45400</v>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I89" s="3">
-        <v>44000</v>
+        <v>45100</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -3702,17 +3919,20 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3">
         <v>1700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3728,13 +3948,14 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3769,8 +3990,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3810,8 +4034,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3851,8 +4078,11 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3868,8 +4098,8 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3">
-        <v>-16200</v>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I94" s="3">
         <v>-16100</v>
@@ -3883,17 +4113,20 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3909,8 +4142,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3950,8 +4184,11 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3991,8 +4228,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4032,8 +4272,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4073,8 +4316,11 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4102,20 +4348,23 @@
       <c r="K100" s="3">
         <v>0</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4155,8 +4404,11 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4172,11 +4424,11 @@
       <c r="G102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H102" s="3">
-        <v>29200</v>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I102" s="3">
-        <v>27900</v>
+        <v>29000</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
@@ -4187,13 +4439,16 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,210 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3400</v>
       </c>
-      <c r="E8" s="3">
-        <v>4900</v>
-      </c>
       <c r="F8" s="3">
-        <v>900</v>
+        <v>5000</v>
       </c>
       <c r="G8" s="3">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="3">
-        <v>3600</v>
+        <v>2000</v>
       </c>
       <c r="I8" s="3">
-        <v>4700</v>
+        <v>3700</v>
       </c>
       <c r="J8" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K8" s="3">
         <v>60800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>41600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>45500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="E9" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4200</v>
-      </c>
       <c r="H9" s="3">
-        <v>1800</v>
+        <v>4300</v>
       </c>
       <c r="I9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J9" s="3">
         <v>2800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>9300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1200</v>
+        <v>11600</v>
       </c>
       <c r="E10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>3000</v>
       </c>
-      <c r="F10" s="3">
-        <v>-1100</v>
-      </c>
       <c r="G10" s="3">
-        <v>-2300</v>
+        <v>-1200</v>
       </c>
       <c r="H10" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>51500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>18400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,52 +889,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>5000</v>
+        <v>1900</v>
       </c>
       <c r="E12" s="3">
-        <v>1900</v>
+        <v>5200</v>
       </c>
       <c r="F12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
-        <v>1200</v>
-      </c>
       <c r="H12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I12" s="3">
         <v>1100</v>
       </c>
-      <c r="I12" s="3">
-        <v>1400</v>
-      </c>
       <c r="J12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,8 +981,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1008,8 +1028,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,17 +1051,17 @@
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I15" s="3">
-        <v>49100</v>
+      <c r="I15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J15" s="3">
+        <v>50100</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1046,14 +1069,17 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,96 +1093,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7400</v>
+        <v>9200</v>
       </c>
       <c r="E17" s="3">
-        <v>5100</v>
+        <v>7500</v>
       </c>
       <c r="F17" s="3">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="G17" s="3">
-        <v>6600</v>
+        <v>4900</v>
       </c>
       <c r="H17" s="3">
-        <v>3800</v>
+        <v>6800</v>
       </c>
       <c r="I17" s="3">
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="J17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K17" s="3">
         <v>16300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4000</v>
+        <v>8200</v>
       </c>
       <c r="E18" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3900</v>
       </c>
-      <c r="G18" s="3">
-        <v>-4700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>44500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,52 +1206,56 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1500</v>
-      </c>
-      <c r="F20" s="3">
-        <v>700</v>
       </c>
       <c r="G20" s="3">
         <v>800</v>
       </c>
       <c r="H20" s="3">
+        <v>800</v>
+      </c>
+      <c r="I20" s="3">
         <v>1100</v>
       </c>
-      <c r="I20" s="3">
-        <v>1900</v>
-      </c>
       <c r="J20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K20" s="3">
         <v>4200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
       </c>
       <c r="M20" s="3">
         <v>200</v>
       </c>
       <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1237,46 +1274,49 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
-        <v>2300</v>
+      <c r="I21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K21" s="3">
         <v>48800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>27500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1299,93 +1339,99 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-3100</v>
-      </c>
       <c r="G23" s="3">
-        <v>-3900</v>
+        <v>-3200</v>
       </c>
       <c r="H23" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="I23" s="3">
         <v>900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>27400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-1400</v>
+        <v>1800</v>
       </c>
       <c r="E24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1393,8 +1439,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,96 +1486,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2000</v>
+        <v>7100</v>
       </c>
       <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>1100</v>
       </c>
-      <c r="F26" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G26" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="I26" s="3">
-        <v>1700</v>
-      </c>
       <c r="J26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K26" s="3">
         <v>47300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>27400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2000</v>
+        <v>7100</v>
       </c>
       <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>1100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G27" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H27" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="I27" s="3">
-        <v>1700</v>
-      </c>
       <c r="J27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K27" s="3">
         <v>47300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1627,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1674,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1721,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,96 +1768,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-700</v>
       </c>
       <c r="G32" s="3">
         <v>-800</v>
       </c>
       <c r="H32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1100</v>
       </c>
-      <c r="I32" s="3">
-        <v>-1900</v>
-      </c>
       <c r="J32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
       </c>
       <c r="M32" s="3">
         <v>-200</v>
       </c>
       <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2000</v>
+        <v>7100</v>
       </c>
       <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>1100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G33" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H33" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="I33" s="3">
-        <v>1700</v>
-      </c>
       <c r="J33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K33" s="3">
         <v>47300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,101 +1909,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2000</v>
+        <v>7100</v>
       </c>
       <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>1100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G35" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H35" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="I35" s="3">
-        <v>1700</v>
-      </c>
       <c r="J35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K35" s="3">
         <v>47300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2029,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,35 +2048,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>92000</v>
+        <v>90900</v>
       </c>
       <c r="E41" s="3">
-        <v>96000</v>
+        <v>93900</v>
       </c>
       <c r="F41" s="3">
-        <v>97200</v>
+        <v>97900</v>
       </c>
       <c r="G41" s="3">
-        <v>105300</v>
+        <v>99200</v>
       </c>
       <c r="H41" s="3">
-        <v>105300</v>
+        <v>107500</v>
       </c>
       <c r="I41" s="3">
-        <v>98400</v>
+        <v>107500</v>
       </c>
       <c r="J41" s="3">
+        <v>100400</v>
+      </c>
+      <c r="K41" s="3">
         <v>97100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,23 +2093,26 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E42" s="3">
         <v>700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>500</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2038,8 +2128,8 @@
       <c r="L42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -2050,8 +2140,11 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2070,12 +2163,12 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>200</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,35 +2187,38 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4200</v>
+        <v>5700</v>
       </c>
       <c r="E44" s="3">
-        <v>5800</v>
+        <v>4300</v>
       </c>
       <c r="F44" s="3">
-        <v>7700</v>
+        <v>5900</v>
       </c>
       <c r="G44" s="3">
-        <v>9700</v>
+        <v>7900</v>
       </c>
       <c r="H44" s="3">
-        <v>11600</v>
+        <v>9900</v>
       </c>
       <c r="I44" s="3">
-        <v>10700</v>
+        <v>11800</v>
       </c>
       <c r="J44" s="3">
+        <v>11000</v>
+      </c>
+      <c r="K44" s="3">
         <v>10600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2138,35 +2234,38 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5100</v>
+        <v>8400</v>
       </c>
       <c r="E45" s="3">
-        <v>6500</v>
+        <v>5200</v>
       </c>
       <c r="F45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2700</v>
-      </c>
       <c r="I45" s="3">
-        <v>5600</v>
+        <v>2800</v>
       </c>
       <c r="J45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="K45" s="3">
         <v>5900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2182,35 +2281,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>102100</v>
+        <v>107400</v>
       </c>
       <c r="E46" s="3">
-        <v>110200</v>
+        <v>104200</v>
       </c>
       <c r="F46" s="3">
-        <v>106900</v>
+        <v>112400</v>
       </c>
       <c r="G46" s="3">
-        <v>116400</v>
+        <v>109000</v>
       </c>
       <c r="H46" s="3">
-        <v>119600</v>
+        <v>118700</v>
       </c>
       <c r="I46" s="3">
-        <v>114900</v>
+        <v>122000</v>
       </c>
       <c r="J46" s="3">
+        <v>117300</v>
+      </c>
+      <c r="K46" s="3">
         <v>113700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,22 +2328,25 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E47" s="3">
         <v>3300</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
       </c>
       <c r="F47" s="3">
         <v>100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
+      <c r="G47" s="3">
+        <v>100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2258,8 +2363,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2270,8 +2375,11 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2279,26 +2387,26 @@
         <v>7000</v>
       </c>
       <c r="E48" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="F48" s="3">
-        <v>6700</v>
+        <v>7200</v>
       </c>
       <c r="G48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="H48" s="3">
         <v>1200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
-        <v>1100</v>
-      </c>
       <c r="J48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,8 +2422,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2325,8 +2436,8 @@
       <c r="E49" s="3">
         <v>500</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>3</v>
+      <c r="F49" s="3">
+        <v>500</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>3</v>
@@ -2343,8 +2454,8 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2358,8 +2469,11 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2516,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,8 +2563,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2455,26 +2575,26 @@
         <v>19000</v>
       </c>
       <c r="E52" s="3">
-        <v>17500</v>
+        <v>19400</v>
       </c>
       <c r="F52" s="3">
-        <v>18300</v>
+        <v>17900</v>
       </c>
       <c r="G52" s="3">
-        <v>17000</v>
+        <v>18700</v>
       </c>
       <c r="H52" s="3">
+        <v>17400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>15900</v>
+      </c>
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="I52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,8 +2610,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,35 +2657,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>131900</v>
+        <v>153100</v>
       </c>
       <c r="E54" s="3">
-        <v>135300</v>
+        <v>134600</v>
       </c>
       <c r="F54" s="3">
-        <v>132000</v>
+        <v>138100</v>
       </c>
       <c r="G54" s="3">
-        <v>134600</v>
+        <v>134700</v>
       </c>
       <c r="H54" s="3">
-        <v>136200</v>
+        <v>137300</v>
       </c>
       <c r="I54" s="3">
-        <v>131700</v>
+        <v>139000</v>
       </c>
       <c r="J54" s="3">
+        <v>134400</v>
+      </c>
+      <c r="K54" s="3">
         <v>130100</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2704,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2725,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,35 +2744,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>600</v>
+      </c>
+      <c r="E57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,8 +2789,11 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2702,35 +2836,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2200</v>
+        <v>12900</v>
       </c>
       <c r="E59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1600</v>
       </c>
       <c r="H59" s="3">
         <v>1700</v>
       </c>
       <c r="I59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2500</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,35 +2883,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
-        <v>3900</v>
-      </c>
       <c r="F60" s="3">
-        <v>1800</v>
+        <v>4000</v>
       </c>
       <c r="G60" s="3">
         <v>1800</v>
       </c>
       <c r="H60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I60" s="3">
         <v>1900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2800</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,8 +2930,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2834,35 +2977,38 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
       </c>
       <c r="F62" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G62" s="3">
         <v>200</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I62" s="3">
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3024,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3071,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3118,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,34 +3165,37 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2400</v>
+        <v>13500</v>
       </c>
       <c r="E66" s="3">
-        <v>4000</v>
+        <v>2500</v>
       </c>
       <c r="F66" s="3">
-        <v>1900</v>
+        <v>4100</v>
       </c>
       <c r="G66" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="H66" s="3">
         <v>1900</v>
       </c>
       <c r="I66" s="3">
-        <v>2700</v>
+        <v>2000</v>
       </c>
       <c r="J66" s="3">
         <v>2800</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
+      <c r="K66" s="3">
+        <v>2800</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
@@ -3054,8 +3212,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3233,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3278,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3325,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3372,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,35 +3419,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>103300</v>
+        <v>112500</v>
       </c>
       <c r="E72" s="3">
-        <v>105300</v>
+        <v>105400</v>
       </c>
       <c r="F72" s="3">
-        <v>104200</v>
+        <v>107500</v>
       </c>
       <c r="G72" s="3">
-        <v>106800</v>
+        <v>106300</v>
       </c>
       <c r="H72" s="3">
-        <v>109700</v>
+        <v>109000</v>
       </c>
       <c r="I72" s="3">
-        <v>109000</v>
+        <v>111900</v>
       </c>
       <c r="J72" s="3">
+        <v>111200</v>
+      </c>
+      <c r="K72" s="3">
         <v>107300</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3466,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3513,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3560,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,35 +3607,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>129500</v>
+        <v>139500</v>
       </c>
       <c r="E76" s="3">
-        <v>131300</v>
+        <v>132200</v>
       </c>
       <c r="F76" s="3">
-        <v>130100</v>
+        <v>134000</v>
       </c>
       <c r="G76" s="3">
         <v>132700</v>
       </c>
       <c r="H76" s="3">
-        <v>134300</v>
+        <v>135400</v>
       </c>
       <c r="I76" s="3">
-        <v>129000</v>
+        <v>137000</v>
       </c>
       <c r="J76" s="3">
+        <v>131600</v>
+      </c>
+      <c r="K76" s="3">
         <v>127200</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3654,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,101 +3701,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2000</v>
+        <v>7100</v>
       </c>
       <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>1100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-2600</v>
-      </c>
       <c r="G81" s="3">
-        <v>-2800</v>
+        <v>-2700</v>
       </c>
       <c r="H81" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="I81" s="3">
-        <v>1700</v>
-      </c>
       <c r="J81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K81" s="3">
         <v>47300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,31 +3821,32 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3658,17 +3857,20 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3913,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3960,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4007,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4054,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,31 +4101,34 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>45100</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3922,17 +4139,20 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>1700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4169,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3993,8 +4214,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4261,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,31 +4308,34 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-16100</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4116,17 +4346,20 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4376,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4187,8 +4421,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4468,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4515,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,8 +4562,11 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4351,20 +4597,23 @@
       <c r="L100" s="3">
         <v>0</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4407,31 +4656,34 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>29000</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -4442,13 +4694,16 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>2200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,223 +656,236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>17300</v>
+        <v>8600</v>
       </c>
       <c r="E8" s="3">
+        <v>16900</v>
+      </c>
+      <c r="F8" s="3">
         <v>3400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5000</v>
       </c>
-      <c r="G8" s="3">
-        <v>1000</v>
-      </c>
       <c r="H8" s="3">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="I8" s="3">
-        <v>3700</v>
+        <v>1900</v>
       </c>
       <c r="J8" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K8" s="3">
         <v>4800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>60800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>21500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>41600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>45500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>5800</v>
+        <v>2800</v>
       </c>
       <c r="E9" s="3">
-        <v>2200</v>
+        <v>5600</v>
       </c>
       <c r="F9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G9" s="3">
         <v>2000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2100</v>
       </c>
-      <c r="H9" s="3">
-        <v>4300</v>
-      </c>
       <c r="I9" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J9" s="3">
         <v>1900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>11600</v>
+        <v>5800</v>
       </c>
       <c r="E10" s="3">
-        <v>1300</v>
+        <v>11300</v>
       </c>
       <c r="F10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G10" s="3">
         <v>3000</v>
       </c>
-      <c r="G10" s="3">
-        <v>-1200</v>
-      </c>
       <c r="H10" s="3">
-        <v>-2400</v>
+        <v>-1100</v>
       </c>
       <c r="I10" s="3">
-        <v>1800</v>
+        <v>-2300</v>
       </c>
       <c r="J10" s="3">
         <v>1900</v>
       </c>
       <c r="K10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L10" s="3">
         <v>51500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,55 +903,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="E12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="F12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K12" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,31 +1001,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1031,40 +1051,43 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>100</v>
+      </c>
+      <c r="G15" s="3">
+        <v>100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>100</v>
       </c>
       <c r="J15" s="3">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3">
         <v>50100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1072,14 +1095,17 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1094,102 +1120,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9200</v>
+        <v>6300</v>
       </c>
       <c r="E17" s="3">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="F17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="G17" s="3">
-        <v>4900</v>
-      </c>
       <c r="H17" s="3">
-        <v>6800</v>
+        <v>4800</v>
       </c>
       <c r="I17" s="3">
-        <v>3900</v>
+        <v>6600</v>
       </c>
       <c r="J17" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5300</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>8200</v>
+        <v>2300</v>
       </c>
       <c r="E18" s="3">
-        <v>-4100</v>
+        <v>8000</v>
       </c>
       <c r="F18" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-3900</v>
-      </c>
       <c r="H18" s="3">
-        <v>-4800</v>
+        <v>-3800</v>
       </c>
       <c r="I18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>44500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,102 +1240,109 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>700</v>
+        <v>1700</v>
       </c>
       <c r="E20" s="3">
-        <v>600</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M20" s="3">
         <v>1500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>800</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M20" s="3">
-        <v>200</v>
       </c>
       <c r="N20" s="3">
         <v>200</v>
       </c>
       <c r="O20" s="3">
+        <v>200</v>
+      </c>
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-4500</v>
       </c>
       <c r="J21" s="3">
+        <v>500</v>
+      </c>
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>48800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>34700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1100</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1312,20 +1352,20 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1342,99 +1382,105 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8800</v>
+        <v>1200</v>
       </c>
       <c r="E23" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
-        <v>-3200</v>
-      </c>
       <c r="H23" s="3">
-        <v>-4000</v>
+        <v>-3100</v>
       </c>
       <c r="I23" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J23" s="3">
         <v>900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>48600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1800</v>
+        <v>800</v>
       </c>
       <c r="E24" s="3">
-        <v>-1500</v>
+        <v>1700</v>
       </c>
       <c r="F24" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1442,8 +1488,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1489,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E26" s="3">
-        <v>-2100</v>
+        <v>6900</v>
       </c>
       <c r="F26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G26" s="3">
         <v>1100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H26" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="I26" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J26" s="3">
         <v>700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>47300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>27400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>34700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E27" s="3">
-        <v>-2100</v>
+        <v>6900</v>
       </c>
       <c r="F27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G27" s="3">
         <v>1100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H27" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="I27" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J27" s="3">
         <v>700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>47300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>34700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1630,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1724,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1771,102 +1838,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-700</v>
+        <v>-1700</v>
       </c>
       <c r="E32" s="3">
-        <v>-600</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>700</v>
+      </c>
+      <c r="G32" s="3">
+        <v>900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>200</v>
+      </c>
+      <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-4200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-200</v>
       </c>
       <c r="N32" s="3">
         <v>-200</v>
       </c>
       <c r="O32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E33" s="3">
-        <v>-2100</v>
+        <v>6900</v>
       </c>
       <c r="F33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>1100</v>
       </c>
-      <c r="G33" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H33" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="I33" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J33" s="3">
         <v>700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>47300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>34700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1912,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E35" s="3">
-        <v>-2100</v>
+        <v>6900</v>
       </c>
       <c r="F35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>1100</v>
       </c>
-      <c r="G35" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H35" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="I35" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J35" s="3">
         <v>700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>47300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>34700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2030,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2049,38 +2135,39 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>90900</v>
+        <v>73300</v>
       </c>
       <c r="E41" s="3">
-        <v>93900</v>
+        <v>88800</v>
       </c>
       <c r="F41" s="3">
-        <v>97900</v>
+        <v>92200</v>
       </c>
       <c r="G41" s="3">
-        <v>99200</v>
+        <v>98000</v>
       </c>
       <c r="H41" s="3">
-        <v>107500</v>
+        <v>96400</v>
       </c>
       <c r="I41" s="3">
-        <v>107500</v>
+        <v>105100</v>
       </c>
       <c r="J41" s="3">
+        <v>111000</v>
+      </c>
+      <c r="K41" s="3">
         <v>100400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>97100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,31 +2183,34 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>500</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2131,8 +2221,8 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2143,8 +2233,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2157,8 +2250,8 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>1400</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -2166,12 +2259,12 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,38 +2283,41 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5700</v>
+        <v>12500</v>
       </c>
       <c r="E44" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F44" s="3">
         <v>4300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="G44" s="3">
-        <v>7900</v>
-      </c>
       <c r="H44" s="3">
-        <v>9900</v>
+        <v>7700</v>
       </c>
       <c r="I44" s="3">
-        <v>11800</v>
+        <v>9700</v>
       </c>
       <c r="J44" s="3">
+        <v>12200</v>
+      </c>
+      <c r="K44" s="3">
         <v>11000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10600</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2237,38 +2333,41 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8400</v>
+        <v>11100</v>
       </c>
       <c r="E45" s="3">
-        <v>5200</v>
+        <v>8200</v>
       </c>
       <c r="F45" s="3">
-        <v>6700</v>
+        <v>5100</v>
       </c>
       <c r="G45" s="3">
-        <v>1500</v>
+        <v>5300</v>
       </c>
       <c r="H45" s="3">
         <v>1400</v>
       </c>
       <c r="I45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J45" s="3">
         <v>2800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,38 +2383,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>107400</v>
+        <v>103900</v>
       </c>
       <c r="E46" s="3">
-        <v>104200</v>
+        <v>104800</v>
       </c>
       <c r="F46" s="3">
-        <v>112400</v>
+        <v>102300</v>
       </c>
       <c r="G46" s="3">
-        <v>109000</v>
+        <v>112500</v>
       </c>
       <c r="H46" s="3">
-        <v>118700</v>
+        <v>106000</v>
       </c>
       <c r="I46" s="3">
-        <v>122000</v>
+        <v>116100</v>
       </c>
       <c r="J46" s="3">
+        <v>126000</v>
+      </c>
+      <c r="K46" s="3">
         <v>117300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>113700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2331,22 +2433,25 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>19100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>3300</v>
-      </c>
-      <c r="F47" s="3">
-        <v>100</v>
-      </c>
-      <c r="G47" s="3">
-        <v>100</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -2366,8 +2471,8 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -2378,38 +2483,41 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7000</v>
+        <v>7200</v>
       </c>
       <c r="E48" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F48" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6900</v>
-      </c>
       <c r="H48" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
-        <v>1000</v>
-      </c>
       <c r="J48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2425,8 +2533,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2439,17 +2550,17 @@
       <c r="F49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="G49" s="3">
+        <v>500</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2457,8 +2568,8 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2472,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2519,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2566,38 +2683,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>34300</v>
+      </c>
+      <c r="F52" s="3">
         <v>19000</v>
       </c>
-      <c r="E52" s="3">
-        <v>19400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>17900</v>
-      </c>
       <c r="G52" s="3">
-        <v>18700</v>
+        <v>16100</v>
       </c>
       <c r="H52" s="3">
-        <v>17400</v>
+        <v>16500</v>
       </c>
       <c r="I52" s="3">
         <v>15900</v>
       </c>
       <c r="J52" s="3">
+        <v>16400</v>
+      </c>
+      <c r="K52" s="3">
         <v>15900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2660,38 +2783,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>153100</v>
+        <v>151900</v>
       </c>
       <c r="E54" s="3">
-        <v>134600</v>
+        <v>149400</v>
       </c>
       <c r="F54" s="3">
+        <v>132300</v>
+      </c>
+      <c r="G54" s="3">
         <v>138100</v>
       </c>
-      <c r="G54" s="3">
-        <v>134700</v>
-      </c>
       <c r="H54" s="3">
-        <v>137300</v>
+        <v>131000</v>
       </c>
       <c r="I54" s="3">
-        <v>139000</v>
+        <v>134300</v>
       </c>
       <c r="J54" s="3">
+        <v>143500</v>
+      </c>
+      <c r="K54" s="3">
         <v>134400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>130100</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2707,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2726,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2745,38 +2875,39 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,31 +2923,34 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2839,38 +2973,41 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12900</v>
+        <v>6900</v>
       </c>
       <c r="E59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>100</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
-        <v>3900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2300</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2886,38 +3023,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>13500</v>
+        <v>10100</v>
       </c>
       <c r="E60" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F60" s="3">
         <v>2400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1800</v>
       </c>
       <c r="H60" s="3">
         <v>1800</v>
       </c>
       <c r="I60" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="J60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K60" s="3">
         <v>2700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2800</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2933,8 +3073,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2945,16 +3088,16 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2980,38 +3123,41 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
-        <v>100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>200</v>
-      </c>
-      <c r="H62" s="3">
-        <v>200</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>100</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3074,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3121,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3168,37 +3323,40 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13500</v>
+        <v>10100</v>
       </c>
       <c r="E66" s="3">
-        <v>2500</v>
+        <v>13200</v>
       </c>
       <c r="F66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G66" s="3">
         <v>4100</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2000</v>
       </c>
       <c r="H66" s="3">
         <v>1900</v>
       </c>
       <c r="I66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J66" s="3">
         <v>2000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>2800</v>
       </c>
       <c r="K66" s="3">
         <v>2800</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
+      <c r="L66" s="3">
+        <v>2800</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
@@ -3215,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3234,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3281,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3328,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3375,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3422,38 +3593,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>112500</v>
+        <v>114200</v>
       </c>
       <c r="E72" s="3">
-        <v>105400</v>
+        <v>109800</v>
       </c>
       <c r="F72" s="3">
+        <v>103600</v>
+      </c>
+      <c r="G72" s="3">
         <v>107500</v>
       </c>
-      <c r="G72" s="3">
-        <v>106300</v>
-      </c>
       <c r="H72" s="3">
-        <v>109000</v>
+        <v>103400</v>
       </c>
       <c r="I72" s="3">
-        <v>111900</v>
+        <v>106600</v>
       </c>
       <c r="J72" s="3">
+        <v>115600</v>
+      </c>
+      <c r="K72" s="3">
         <v>111200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>107300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3469,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3516,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3563,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3610,38 +3793,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>139500</v>
+        <v>141700</v>
       </c>
       <c r="E76" s="3">
-        <v>132200</v>
+        <v>136200</v>
       </c>
       <c r="F76" s="3">
+        <v>129800</v>
+      </c>
+      <c r="G76" s="3">
         <v>134000</v>
       </c>
-      <c r="G76" s="3">
-        <v>132700</v>
-      </c>
       <c r="H76" s="3">
-        <v>135400</v>
+        <v>129000</v>
       </c>
       <c r="I76" s="3">
-        <v>137000</v>
+        <v>132400</v>
       </c>
       <c r="J76" s="3">
+        <v>141500</v>
+      </c>
+      <c r="K76" s="3">
         <v>131600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>127200</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3657,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3704,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7100</v>
+        <v>400</v>
       </c>
       <c r="E81" s="3">
-        <v>-2100</v>
+        <v>6900</v>
       </c>
       <c r="F81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>1100</v>
       </c>
-      <c r="G81" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H81" s="3">
-        <v>-2900</v>
+        <v>-2600</v>
       </c>
       <c r="I81" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J81" s="3">
         <v>700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>47300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>34700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3822,34 +4020,35 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
@@ -3860,17 +4059,20 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3916,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3963,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4010,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4057,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4104,34 +4318,37 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
       </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
@@ -4142,17 +4359,20 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3">
         <v>1700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4170,31 +4390,32 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4217,8 +4438,11 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4264,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4311,34 +4538,37 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
@@ -4349,17 +4579,20 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4377,31 +4610,32 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4424,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4471,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4518,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4565,31 +4808,34 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -4600,43 +4846,46 @@
       <c r="M100" s="3">
         <v>0</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4659,8 +4908,11 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4685,8 +4937,8 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -4697,13 +4949,16 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,236 +656,248 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E8" s="3">
         <v>8600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>60800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>21500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>41600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>45500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E9" s="3">
         <v>2800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E10" s="3">
         <v>5800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-2300</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1900</v>
       </c>
       <c r="K10" s="3">
         <v>1900</v>
       </c>
       <c r="L10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M10" s="3">
         <v>51500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>32500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,58 +916,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1200</v>
       </c>
       <c r="J12" s="3">
         <v>1200</v>
       </c>
       <c r="K12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="L12" s="3">
         <v>1500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,13 +1020,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-4000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1018,11 +1037,11 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1030,8 +1049,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1054,8 +1073,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1081,16 +1103,16 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>100</v>
+      </c>
+      <c r="L15" s="3">
         <v>50100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1098,14 +1120,17 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,108 +1146,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>16300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>44500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>34500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,108 +1273,115 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>4200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
-      </c>
-      <c r="N20" s="3">
-        <v>200</v>
       </c>
       <c r="O20" s="3">
         <v>200</v>
       </c>
       <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-4500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>48800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>27500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>34700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1355,20 +1394,20 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1385,105 +1424,111 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1491,8 +1536,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1589,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>47300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>34700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>47300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>34700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1748,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1801,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1854,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,108 +1907,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-4200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-200</v>
       </c>
       <c r="O32" s="3">
         <v>-200</v>
       </c>
       <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>47300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>34700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2066,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>47300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>34700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2200,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,41 +2221,42 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E41" s="3">
         <v>73300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>88800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>92200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>96400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>100400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>97100</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,34 +2272,37 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E42" s="3">
         <v>7000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>500</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
+      <c r="K42" s="3">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>3</v>
@@ -2224,8 +2313,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2236,8 +2325,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2250,24 +2342,24 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3">
         <v>1400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,41 +2378,44 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E44" s="3">
         <v>12500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>11000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2336,41 +2431,44 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E45" s="3">
         <v>11100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,41 +2484,44 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E46" s="3">
         <v>103900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>104800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>112500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>106000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>116100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>126000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>117300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>113700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,13 +2537,16 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>2800</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>3</v>
@@ -2474,8 +2578,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2486,41 +2590,44 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E48" s="3">
         <v>7200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,8 +2643,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2554,7 +2664,7 @@
         <v>500</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -2562,8 +2672,8 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2571,8 +2681,8 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2586,8 +2696,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2749,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,41 +2802,44 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E52" s="3">
         <v>37500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15600</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2736,8 +2855,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,41 +2908,44 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E54" s="3">
         <v>151900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>149400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>132300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>138100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>131000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>134300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>143500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>134400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>130100</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2961,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2984,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,41 +3005,42 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,13 +3056,16 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -2944,7 +3077,7 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>100</v>
@@ -2953,7 +3086,7 @@
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2976,41 +3109,44 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E59" s="3">
         <v>6900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,41 +3162,44 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E60" s="3">
         <v>10100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3215,11 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3088,19 +3230,19 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
         <v>100</v>
       </c>
       <c r="H61" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I61" s="3">
         <v>200</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3126,8 +3268,11 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3152,15 +3297,15 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3321,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3374,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3427,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,40 +3480,43 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E66" s="3">
         <v>10100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4100</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1900</v>
       </c>
       <c r="I66" s="3">
         <v>1900</v>
       </c>
       <c r="J66" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K66" s="3">
         <v>2000</v>
-      </c>
-      <c r="K66" s="3">
-        <v>2800</v>
       </c>
       <c r="L66" s="3">
         <v>2800</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
+      <c r="M66" s="3">
+        <v>2800</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
@@ -3376,8 +3533,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3556,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3607,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3660,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3713,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,41 +3766,44 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E72" s="3">
         <v>114200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>109800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>103600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>107500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>103400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>106600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>111200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>107300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3819,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3872,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3925,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,41 +3978,44 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E76" s="3">
         <v>141700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>136200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>129800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>134000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>129000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>132400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>141500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>131600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>127200</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4031,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4084,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>47300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>34700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4218,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4035,23 +4233,23 @@
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -4062,17 +4260,20 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4322,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4375,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4428,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4481,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,8 +4534,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4347,11 +4563,11 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -4362,17 +4578,20 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,8 +4610,9 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4417,8 +4637,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -4441,8 +4661,11 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4714,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,8 +4767,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4567,11 +4796,11 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4582,17 +4811,20 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4843,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4637,8 +4870,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -4661,8 +4894,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4947,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5000,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,8 +5053,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4837,8 +5082,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -4849,20 +5094,23 @@
       <c r="N100" s="3">
         <v>0</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4887,8 +5135,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4911,8 +5159,11 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4940,8 +5191,8 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4952,13 +5203,16 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -1029,7 +1029,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4000</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1082,7 +1082,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1280,7 +1280,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1000</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
         <v>1700</v>
@@ -1333,7 +1333,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-3900</v>
+        <v>100</v>
       </c>
       <c r="E21" s="3">
         <v>800</v>
@@ -1385,8 +1385,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1916,7 +1916,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
         <v>-1700</v>
@@ -2228,7 +2228,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>48500</v>
+        <v>44100</v>
       </c>
       <c r="E41" s="3">
         <v>73300</v>
@@ -2240,7 +2240,7 @@
         <v>92200</v>
       </c>
       <c r="H41" s="3">
-        <v>98000</v>
+        <v>82500</v>
       </c>
       <c r="I41" s="3">
         <v>96400</v>
@@ -2293,7 +2293,7 @@
         <v>700</v>
       </c>
       <c r="H42" s="3">
-        <v>1900</v>
+        <v>14600</v>
       </c>
       <c r="I42" s="3">
         <v>500</v>
@@ -2333,8 +2333,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>300</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
@@ -2440,7 +2440,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>9500</v>
+        <v>13600</v>
       </c>
       <c r="E45" s="3">
         <v>11100</v>
@@ -2505,7 +2505,7 @@
         <v>102300</v>
       </c>
       <c r="H46" s="3">
-        <v>112500</v>
+        <v>109600</v>
       </c>
       <c r="I46" s="3">
         <v>106000</v>
@@ -2557,8 +2557,8 @@
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
+      <c r="H47" s="3">
+        <v>2800</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
@@ -3118,7 +3118,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="E59" s="3">
         <v>6900</v>

--- a/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ICG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="92">
   <si>
     <t>ICG</t>
   </si>
@@ -656,248 +656,274 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F8" s="3">
         <v>10200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>8600</v>
       </c>
-      <c r="F8" s="3">
-        <v>16900</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>3400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>3800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>60800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>21500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>41600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>45500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F9" s="3">
         <v>7500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2800</v>
       </c>
-      <c r="F9" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2000</v>
+      <c r="H9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I9" s="3">
         <v>2100</v>
       </c>
       <c r="J9" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K9" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L9" s="3">
         <v>4200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>9300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>9200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>6600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>3200</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F10" s="3">
         <v>2700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5800</v>
       </c>
-      <c r="F10" s="3">
-        <v>11300</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="3">
         <v>1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>3000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-1100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>51500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>18400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>32500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>39000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>2800</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,61 +943,69 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F12" s="3">
         <v>6300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P12" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>3800</v>
+      </c>
+      <c r="R12" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="G12" s="3">
-        <v>5100</v>
-      </c>
-      <c r="H12" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M12" s="3">
-        <v>5200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>700</v>
-      </c>
-      <c r="O12" s="3">
-        <v>3800</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3500</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1800</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,40 +1057,46 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1076,25 +1116,31 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
-        <v>100</v>
-      </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1106,31 +1152,37 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>50100</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>50100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,114 +1199,128 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F17" s="3">
         <v>15200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6300</v>
       </c>
-      <c r="F17" s="3">
-        <v>8900</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3">
         <v>8100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>16300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>14400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>11100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5300</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-5000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>2300</v>
       </c>
-      <c r="F18" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3">
         <v>-4800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>44500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>17000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>27200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>34500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,131 +1340,145 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-5000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-3900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>48800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>27500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>34700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1100</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
@@ -1412,8 +1492,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1427,120 +1507,138 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
-        <v>8600</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3">
         <v>-3500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>48600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>18500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>27400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>34700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,114 +1690,132 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3">
         <v>-2000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>47300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>17800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>27400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>34700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3">
         <v>-2000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>47300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>17800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>27400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>34700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1926,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,114 +2044,132 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="F32" s="3">
         <v>5000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>700</v>
+      </c>
+      <c r="J32" s="3">
+        <v>900</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>900</v>
-      </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3">
         <v>-2000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>47300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>17800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>27400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>34700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,119 +2221,137 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3">
         <v>-2000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>47300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>17800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>27400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>34700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,47 +2394,49 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
+        <v>33500</v>
+      </c>
+      <c r="F41" s="3">
         <v>44100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>73300</v>
       </c>
-      <c r="F41" s="3">
-        <v>88800</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>92200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>82500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>96400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>105100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>111000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>100400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>97100</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,40 +2449,46 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F42" s="3">
         <v>27200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>7000</v>
       </c>
-      <c r="F42" s="3">
-        <v>2300</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>14600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>500</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2316,11 +2496,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2328,44 +2508,50 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
         <v>1400</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2381,47 +2567,53 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12700</v>
+      </c>
+      <c r="F44" s="3">
         <v>13500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>12500</v>
       </c>
-      <c r="F44" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3">
         <v>4300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>7700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>9700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>12200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>11000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>10600</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2434,47 +2626,53 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F45" s="3">
         <v>13600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11100</v>
       </c>
-      <c r="F45" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>5100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,47 +2685,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3">
+        <v>99100</v>
+      </c>
+      <c r="F46" s="3">
         <v>98800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>103900</v>
       </c>
-      <c r="F46" s="3">
-        <v>104800</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>102300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>109600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>106000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>116100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>126000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>117300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>113700</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2540,32 +2744,38 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2800</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>2800</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2581,11 +2791,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -2593,47 +2803,53 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F48" s="3">
         <v>21600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>7100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>7200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>6700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1100</v>
       </c>
       <c r="L48" s="3">
         <v>1200</v>
       </c>
       <c r="M48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,13 +2862,19 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>500</v>
+      <c r="D49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E49" s="3">
         <v>500</v>
@@ -2663,32 +2885,32 @@
       <c r="G49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2699,8 +2921,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,47 +3039,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F52" s="3">
         <v>21700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>37500</v>
       </c>
-      <c r="F52" s="3">
-        <v>34300</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>19000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>16100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>16500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>16400</v>
       </c>
       <c r="L52" s="3">
         <v>15900</v>
       </c>
       <c r="M52" s="3">
+        <v>16400</v>
+      </c>
+      <c r="N52" s="3">
+        <v>15900</v>
+      </c>
+      <c r="O52" s="3">
         <v>15600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +3098,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,47 +3157,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3">
+        <v>143100</v>
+      </c>
+      <c r="F54" s="3">
         <v>149300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>151900</v>
       </c>
-      <c r="F54" s="3">
-        <v>149400</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>132300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>138100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>131000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>134300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>143500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>134400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>130100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3216,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,47 +3266,49 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
-        <v>600</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,40 +3321,46 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
-        <v>100</v>
-      </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3112,47 +3380,53 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F59" s="3">
         <v>6400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>6900</v>
       </c>
-      <c r="F59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,47 +3439,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F60" s="3">
         <v>10500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10100</v>
       </c>
-      <c r="F60" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>2400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,8 +3498,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3233,23 +3519,23 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3271,8 +3557,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3300,18 +3592,18 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3616,14 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,47 +3793,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F66" s="3">
         <v>10500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>10100</v>
       </c>
-      <c r="F66" s="3">
-        <v>13200</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>2400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2800</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3852,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,47 +4111,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
+        <v>107500</v>
+      </c>
+      <c r="F72" s="3">
         <v>111500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>114200</v>
       </c>
-      <c r="F72" s="3">
-        <v>109800</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>103600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>107500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>103400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>106600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>115600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>111200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>107300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +4170,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,47 +4347,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3">
+        <v>135800</v>
+      </c>
+      <c r="F76" s="3">
         <v>138800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>141700</v>
       </c>
-      <c r="F76" s="3">
-        <v>136200</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3">
         <v>129800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>134000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>129000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>132400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>141500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>131600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>127200</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4406,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,119 +4465,137 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3">
         <v>-2000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>47300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>17800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>27400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>34700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,8 +4615,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4236,26 +4634,26 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4263,17 +4661,23 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,8 +4965,14 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4566,14 +5000,14 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4581,17 +5015,23 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3">
         <v>1700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,8 +5051,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4640,11 +5082,11 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -4664,8 +5106,14 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,8 +5224,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4799,14 +5259,14 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4814,17 +5274,23 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5310,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4873,11 +5341,11 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -4897,8 +5365,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,8 +5542,14 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5085,11 +5577,11 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -5097,20 +5589,26 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5138,11 +5636,11 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -5162,8 +5660,14 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5194,11 +5698,11 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -5206,13 +5710,19 @@
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3">
         <v>2200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
